--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2649,7 +2649,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2675-29-CM26</t>
+          <t>1375760-6-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>61.981.310-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA VALLE CACHAPOAL</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>53849.29</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3838-26-CM26</t>
+          <t>2675-29-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>33023.45</v>
+        <v>53849.29</v>
       </c>
     </row>
     <row r="39">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3507,7 +3507,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3838-123-CM26</t>
+          <t>557639-614-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4226.88</v>
+        <v>1479.41</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>557639-614-CM26</t>
+          <t>1622-657-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>79.770.640-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3623,13 +3623,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1479.41</v>
+        <v>1123.87</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1622-657-CM26</t>
+          <t>3863-185-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>COMPUTACION GRAFICA APLICADA Y CIA LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>79.770.640-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1123.87</v>
+        <v>7819.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3863-185-CM26</t>
+          <t>3598-519-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>69.091.300-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>92.580.000-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3745,13 +3745,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7819.29</v>
+        <v>16041.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3598-519-CM26</t>
+          <t>889473-1191-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3766,22 +3766,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.091.300-3</t>
+          <t>61.980.530-5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARCHIGUE</t>
+          <t>UNIVERSIDAD DE O'HIGGINS</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>92.580.000-7</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>16041.2</v>
+        <v>8182.44</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>889473-1191-CM26</t>
+          <t>3996-373-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.980.530-5</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE O'HIGGINS</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3867,13 +3867,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>8182.44</v>
+        <v>7983.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3996-373-CM26</t>
+          <t>3731-192-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.080.700-9</t>
+          <t>69.090.300-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
+          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3913,12 +3913,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>7983.23</v>
+        <v>6886.53</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3731-192-CM26</t>
+          <t>3690-213-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.090.300-8</t>
+          <t>69.080.800-5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHIMBARONGO</t>
+          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Inversiones Hebo Limitada</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>77.553.790-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3989,13 +3989,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6886.53</v>
+        <v>14779.8</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3690-213-CM26</t>
+          <t>3946-315-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.080.800-5</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CABRAS</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4035,12 +4035,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Inversiones Hebo Limitada</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.553.790-6</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>14779.8</v>
+        <v>1377.31</v>
       </c>
     </row>
     <row r="60">
@@ -4117,7 +4117,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3946-315-CM26</t>
+          <t>3997-306-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>69.080.700-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>I MUNICIPALIDAD DE COLTAUCO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Netsus SpA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4172,67 +4172,6 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1377.31</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>3997-306-CM26</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2239-11-LR24</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>69.080.700-9</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE COLTAUCO</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>TECNOLOGIA BS SPA</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>76.852.815-2</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="n">
         <v>14635.93</v>
       </c>
     </row>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
@@ -562,7 +562,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.899.890-0</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>76.232.892-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1663,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1728,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1793,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1858,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1923,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1988,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2053,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2118,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2183,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2248,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2313,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2378,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2443,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2508,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2573,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2638,11 @@
           <t>76.449.580-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2703,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2768,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2833,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2898,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2963,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3028,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3093,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3158,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3288,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3353,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3479,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3605,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3670,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3735,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3861,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3926,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3799,7 +3991,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4056,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3921,7 +4121,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4186,11 @@
           <t>77.553.790-6</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4251,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4316,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4381,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/o-higgins.xlsx
@@ -2610,7 +2610,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
